--- a/Assets/Excel/items.xlsx
+++ b/Assets/Excel/items.xlsx
@@ -1,9 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="21525" windowHeight="12270"/>
+  </bookViews>
   <sheets>
-    <sheet name="items" sheetId="1" r:id="rId2"/>
+    <sheet name="items" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -144,10 +163,1164 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="8.875" customWidth="1"/>
+    <col min="3" max="3" width="8.375" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -161,7 +1334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -175,7 +1348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -189,7 +1362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -203,7 +1376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -217,7 +1390,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -231,7 +1404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -245,7 +1418,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -259,7 +1432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -273,7 +1446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -287,7 +1460,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -302,5 +1475,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excel/items.xlsx
+++ b/Assets/Excel/items.xlsx
@@ -1,14 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="21525" windowHeight="12270"/>
+  </bookViews>
   <sheets>
-    <sheet name="items" sheetId="1" r:id="rId2"/>
+    <sheet name="items" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
   <si>
     <t>道具ID</t>
   </si>
@@ -188,14 +207,1243 @@
   </si>
   <si>
     <t>黑松林深处的铁木，砍起来费劲，木质却密实如铁。</t>
+  </si>
+  <si>
+    <t>small_trap</t>
+  </si>
+  <si>
+    <t>小陷阱</t>
+  </si>
+  <si>
+    <t>#8A7058</t>
+  </si>
+  <si>
+    <t>简易绳套与木刺，魔物探索时布置在林缘与溪谷。</t>
+  </si>
+  <si>
+    <t>large_trap</t>
+  </si>
+  <si>
+    <t>大陷阱</t>
+  </si>
+  <si>
+    <t>#6A5848</t>
+  </si>
+  <si>
+    <t>铁夹与粗绳编成，能困住更强壮的魔物，用于危险地带。</t>
+  </si>
+  <si>
+    <t>slime_gel</t>
+  </si>
+  <si>
+    <t>史莱姆凝胶</t>
+  </si>
+  <si>
+    <t>半透明黏液，炼药常用来调和性状。</t>
+  </si>
+  <si>
+    <t>beast_fang</t>
+  </si>
+  <si>
+    <t>兽牙</t>
+  </si>
+  <si>
+    <t>#E8E0D0</t>
+  </si>
+  <si>
+    <t>从魔物嘴里撬下的尖牙，打磨后可做饰品或刃料。</t>
+  </si>
+  <si>
+    <t>tattered_pelt</t>
+  </si>
+  <si>
+    <t>破烂兽皮</t>
+  </si>
+  <si>
+    <t>#6A5040</t>
+  </si>
+  <si>
+    <t>带着爪痕的皮毛，缝补防具勉强能用。</t>
+  </si>
+  <si>
+    <t>monster_pa</t>
+  </si>
+  <si>
+    <t>奇怪的内裤</t>
+  </si>
+  <si>
+    <t>#7A4A68</t>
+  </si>
+  <si>
+    <t>一条奇怪的内裤。</t>
+  </si>
+  <si>
+    <t>cracked_core</t>
+  </si>
+  <si>
+    <t>裂纹魔核</t>
+  </si>
+  <si>
+    <t>#B888D8</t>
+  </si>
+  <si>
+    <t>魔物核心碎裂后的结晶，仍残留微弱魔力。</t>
   </si>
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -209,7 +1457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -223,7 +1471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -237,7 +1485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -251,7 +1499,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -265,7 +1513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -279,7 +1527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -293,7 +1541,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -307,7 +1555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -321,7 +1569,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -335,7 +1583,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -349,7 +1597,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -363,7 +1611,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -377,7 +1625,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -391,7 +1639,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -405,6 +1653,106 @@
         <v>59</v>
       </c>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excel/items.xlsx
+++ b/Assets/Excel/items.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
   <si>
     <t>道具ID</t>
   </si>
@@ -68,19 +68,22 @@
     <t>#B89468</t>
   </si>
   <si>
+    <t>item_rag</t>
+  </si>
+  <si>
+    <t>脏兮兮的布条，也许还能缝点什么。</t>
+  </si>
+  <si>
+    <t>splinter</t>
+  </si>
+  <si>
+    <t>碎木</t>
+  </si>
+  <si>
+    <t>#324030</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>脏兮兮的布条，也许还能缝点什么。</t>
-  </si>
-  <si>
-    <t>splinter</t>
-  </si>
-  <si>
-    <t>碎木</t>
-  </si>
-  <si>
-    <t>#324030</t>
   </si>
   <si>
     <t>从废料里捡出的木片，生火或当柄都行。</t>
@@ -1565,384 +1568,384 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/items.xlsx
+++ b/Assets/Excel/items.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>道具ID</t>
   </si>
@@ -32,6 +32,18 @@
   </si>
   <si>
     <t>description</t>
+  </si>
+  <si>
+    <t>_empty</t>
+  </si>
+  <si>
+    <t>（无）</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>掉落表占位：本次未获得道具。</t>
   </si>
   <si>
     <t>rag</t>
@@ -345,189 +357,189 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>62</v>
@@ -541,94 +553,108 @@
         <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/items.xlsx
+++ b/Assets/Excel/items.xlsx
@@ -1,14 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowHeight="17775"/>
+  </bookViews>
   <sheets>
-    <sheet name="items" sheetId="1" r:id="rId2"/>
+    <sheet name="items" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="90">
   <si>
     <t>道具ID</t>
   </si>
@@ -58,43 +77,49 @@
     <t>脏兮兮的布条，也许还能缝点什么。</t>
   </si>
   <si>
-    <t>splinter</t>
-  </si>
-  <si>
-    <t>碎木</t>
+    <t>wood_scraps</t>
+  </si>
+  <si>
+    <t>木头废料</t>
+  </si>
+  <si>
+    <t>item_wood_scraps</t>
+  </si>
+  <si>
+    <t>从废料里捡出的木块，只能去生火了。</t>
+  </si>
+  <si>
+    <t>empty_bottle</t>
+  </si>
+  <si>
+    <t>空瓶</t>
+  </si>
+  <si>
+    <t>item_empty_bottle</t>
+  </si>
+  <si>
+    <t>洗一洗就能装药水的玻璃瓶。</t>
+  </si>
+  <si>
+    <t>copper_nail</t>
+  </si>
+  <si>
+    <t>锈钉子</t>
+  </si>
+  <si>
+    <t>item_copper_nail</t>
+  </si>
+  <si>
+    <t>生锈但还能用的钉子，锻造常缺这个。</t>
+  </si>
+  <si>
+    <t>worn_coin</t>
+  </si>
+  <si>
+    <t>褪色铜币</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>从废料里捡出的木片，生火或当柄都行。</t>
-  </si>
-  <si>
-    <t>empty_bottle</t>
-  </si>
-  <si>
-    <t>空瓶</t>
-  </si>
-  <si>
-    <t>item_empty_bottle</t>
-  </si>
-  <si>
-    <t>洗一洗就能装药水的玻璃瓶。</t>
-  </si>
-  <si>
-    <t>copper_nail</t>
-  </si>
-  <si>
-    <t>铜钉</t>
-  </si>
-  <si>
-    <t>生锈但还能用的钉子，锻造常缺这个。</t>
-  </si>
-  <si>
-    <t>worn_coin</t>
-  </si>
-  <si>
-    <t>褪色铜币</t>
   </si>
   <si>
     <t>磨损的零钱，村里认，也能熔了当铜料。</t>
@@ -276,10 +301,1158 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -293,7 +1466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -307,7 +1480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -321,7 +1494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -335,7 +1508,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -349,7 +1522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -363,7 +1536,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -371,292 +1544,294 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
       <c r="D9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excel/items.xlsx
+++ b/Assets/Excel/items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowWidth="21525" windowHeight="12270"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="89">
   <si>
     <t>道具ID</t>
   </si>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>褪色铜币</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>磨损的零钱，村里认，也能熔了当铜料。</t>
@@ -1558,276 +1555,276 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
         <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
         <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
         <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
         <v>45</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
         <v>48</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
         <v>50</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
         <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
         <v>53</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
         <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
         <v>56</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
         <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
         <v>59</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
         <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
         <v>62</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
         <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s">
         <v>69</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
         <v>72</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
         <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
         <v>75</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
         <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
         <v>78</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
         <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
         <v>81</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
         <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
         <v>84</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
         <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
         <v>87</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
         <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
